--- a/product_surveys/029_new_product_launch_consumer_opinion_poll--product_surveys.xlsx
+++ b/product_surveys/029_new_product_launch_consumer_opinion_poll--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>follow up</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>do_not_follow_up</t>
+          <t>do not follow up</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>not_please</t>
+          <t>not please</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>not_at_all</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>social media</t>
         </is>
       </c>
     </row>
